--- a/fixtures/annotations.xlsx
+++ b/fixtures/annotations.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Link out</t>
   </si>
@@ -60,6 +60,25 @@
   </si>
   <si>
     <t>Second sheet</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFCC0000"/>
+      </rPr>
+      <t xml:space="preserve">Total: </t>
+    </r>
+    <r>
+      <t xml:space="preserve">1234</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+      </rPr>
+      <t xml:space="preserve"> kg</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -126,6 +145,24 @@
         <v>42</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+            </rPr>
+            <t>inline </t>
+          </r>
+          <r>
+            <t>runs</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1"/>
